--- a/experiments/results/reduced_bound/cplex-cp-reduced-bound.xlsx
+++ b/experiments/results/reduced_bound/cplex-cp-reduced-bound.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,25 +445,35 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Lower bound</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Upper bound</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Best bound</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Best objective</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Time consumed (s)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -497,25 +507,35 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>0.19</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -549,25 +569,35 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -601,25 +631,35 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>0.06</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -653,25 +693,35 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>8.9</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>0.92</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -705,25 +755,35 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>6.8</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>0.06</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -757,25 +817,35 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>0.14</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -809,25 +879,35 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>0.15</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -861,25 +941,35 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>22.3</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>54.24</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -913,25 +1003,35 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>323.3</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>1800.00</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -961,25 +1061,35 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>208.7</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>1800.00</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1009,25 +1119,35 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>12.4</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>0.90</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1061,25 +1181,35 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>10.7</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>0.11</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1113,25 +1243,35 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>192</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>132.2</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>1800.04</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1161,25 +1301,35 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>192</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>132.4</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>1800.03</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1209,25 +1359,35 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>182</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>195.1</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>1800.00</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1257,25 +1417,35 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>189</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>139.2</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>1800.00</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1305,25 +1475,35 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>227</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>74.0</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>27.90</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1357,25 +1537,35 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>218</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>187.6</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>1800.02</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1405,25 +1595,35 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>260</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>260</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>141.9</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>755.27</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1457,25 +1657,35 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>117</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>244</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>178.0</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>1800.07</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1505,25 +1715,35 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>331</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>331</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>110.3</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>26.38</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1557,25 +1777,35 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>328</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>331</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>211.1</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>1800.08</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1605,25 +1835,35 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>341</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>206.7</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>1800.07</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1653,25 +1893,35 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>321</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>239.4</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>1800.02</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1684,7 +1934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1715,25 +1965,35 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Lower bound</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Upper bound</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Best bound</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Best objective</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Memory consumed (MB)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Time consumed (s)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Optimal found</t>
         </is>
@@ -1767,25 +2027,35 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>8.8</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>3.24</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1819,25 +2089,35 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>6.8</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>0.12</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1871,25 +2151,35 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>6.7</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>0.09</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1923,25 +2213,35 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>9.3</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>1.00</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -1975,25 +2275,35 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>6.8</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>0.04</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2027,25 +2337,35 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>8.8</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>0.19</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2079,25 +2399,35 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>9.8</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2131,25 +2461,35 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>45.1</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>183.23</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2183,25 +2523,35 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>188.1</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>1800.02</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2231,25 +2581,35 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>69</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>128.9</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>1800.00</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2279,25 +2639,35 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>77</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>17.3</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>18.10</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2331,25 +2701,35 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>13.4</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>0.31</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2383,25 +2763,35 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>307</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>152.9</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>1800.05</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2431,25 +2821,35 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>307</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>153.5</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>1800.04</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2479,25 +2879,35 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>273</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>180.6</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>1800.07</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2527,25 +2937,35 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>147</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>318</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>165.8</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>1800.06</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2575,25 +2995,35 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>341</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>112.6</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>133.20</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2627,25 +3057,35 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>348</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>206.0</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>1800.06</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2675,25 +3115,35 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
           <t>390</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>183.2</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>1800.09</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2723,25 +3173,35 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>392</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>219.3</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>1800.02</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2771,25 +3231,35 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>496</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>496</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>144.6</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>71.13</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>x</t>
         </is>
@@ -2823,25 +3293,35 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
           <t>492</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>242.0</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>1800.10</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2871,25 +3351,35 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
           <t>204</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>511</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>258.4</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>1800.08</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2919,25 +3409,35 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>488</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>276.4</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>1800.02</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
